--- a/artfynd/A 6170-2026 artfynd.xlsx
+++ b/artfynd/A 6170-2026 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131440202</v>
+        <v>131440157</v>
       </c>
       <c r="B2" t="n">
-        <v>79273</v>
+        <v>79868</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>386622</v>
+        <v>386666</v>
       </c>
       <c r="R2" t="n">
-        <v>6758434</v>
+        <v>6758441</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131440157</v>
+        <v>131440202</v>
       </c>
       <c r="B3" t="n">
-        <v>79868</v>
+        <v>79273</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>386666</v>
+        <v>386622</v>
       </c>
       <c r="R3" t="n">
-        <v>6758441</v>
+        <v>6758434</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131440173</v>
+        <v>131440201</v>
       </c>
       <c r="B11" t="n">
-        <v>57076</v>
+        <v>79273</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,42 +1609,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6434</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>386497</v>
+        <v>386642</v>
       </c>
       <c r="R11" t="n">
-        <v>6758307</v>
+        <v>6758467</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1703,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131440201</v>
+        <v>131440175</v>
       </c>
       <c r="B12" t="n">
-        <v>79273</v>
+        <v>57076</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1714,34 +1706,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6434</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>386642</v>
+        <v>386616</v>
       </c>
       <c r="R12" t="n">
-        <v>6758467</v>
+        <v>6758440</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1800,7 +1800,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131440175</v>
+        <v>131440173</v>
       </c>
       <c r="B13" t="n">
         <v>57076</v>
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>386616</v>
+        <v>386497</v>
       </c>
       <c r="R13" t="n">
-        <v>6758440</v>
+        <v>6758307</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2129,45 +2129,53 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131440155</v>
+        <v>131440176</v>
       </c>
       <c r="B16" t="n">
-        <v>79868</v>
+        <v>57076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>386674</v>
+        <v>386587</v>
       </c>
       <c r="R16" t="n">
-        <v>6758410</v>
+        <v>6758386</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2323,53 +2331,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131440176</v>
+        <v>131440155</v>
       </c>
       <c r="B18" t="n">
-        <v>57076</v>
+        <v>79868</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>386587</v>
+        <v>386674</v>
       </c>
       <c r="R18" t="n">
-        <v>6758386</v>
+        <v>6758410</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -3182,53 +3182,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131448249</v>
+        <v>131440153</v>
       </c>
       <c r="B26" t="n">
-        <v>57076</v>
+        <v>79868</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>386523</v>
+        <v>386590</v>
       </c>
       <c r="R26" t="n">
-        <v>6758378</v>
+        <v>6758339</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3255,19 +3250,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3282,60 +3267,65 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131440153</v>
+        <v>131448249</v>
       </c>
       <c r="B27" t="n">
-        <v>79868</v>
+        <v>57076</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>386590</v>
+        <v>386523</v>
       </c>
       <c r="R27" t="n">
-        <v>6758339</v>
+        <v>6758378</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3362,9 +3352,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3379,19 +3379,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131448254</v>
+        <v>131448234</v>
       </c>
       <c r="B28" t="n">
         <v>79249</v>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>386541</v>
+        <v>386438</v>
       </c>
       <c r="R28" t="n">
-        <v>6758426</v>
+        <v>6758131</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3461,7 +3461,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3498,7 +3498,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131448234</v>
+        <v>131448254</v>
       </c>
       <c r="B29" t="n">
         <v>79249</v>
@@ -3533,10 +3533,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>386438</v>
+        <v>386541</v>
       </c>
       <c r="R29" t="n">
-        <v>6758131</v>
+        <v>6758426</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3578,7 +3578,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3605,10 +3605,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131448239</v>
+        <v>131448255</v>
       </c>
       <c r="B30" t="n">
-        <v>79868</v>
+        <v>79249</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3616,21 +3616,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>386487</v>
+        <v>386544</v>
       </c>
       <c r="R30" t="n">
-        <v>6758237</v>
+        <v>6758480</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3712,7 +3712,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131448255</v>
+        <v>131448194</v>
       </c>
       <c r="B31" t="n">
         <v>79249</v>
@@ -3747,10 +3747,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>386544</v>
+        <v>386442</v>
       </c>
       <c r="R31" t="n">
-        <v>6758480</v>
+        <v>6758296</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3792,7 +3792,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3819,10 +3819,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131448242</v>
+        <v>131448239</v>
       </c>
       <c r="B32" t="n">
-        <v>78915</v>
+        <v>79868</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3830,21 +3830,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3854,10 +3854,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>386479</v>
+        <v>386487</v>
       </c>
       <c r="R32" t="n">
-        <v>6758227</v>
+        <v>6758237</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3900,11 +3900,6 @@
       <c r="AB32" t="inlineStr">
         <is>
           <t>14:09</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På stubbe med fem brandljud</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3931,10 +3926,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131448194</v>
+        <v>131448242</v>
       </c>
       <c r="B33" t="n">
-        <v>79249</v>
+        <v>78915</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3942,21 +3937,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3966,10 +3961,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>386442</v>
+        <v>386479</v>
       </c>
       <c r="R33" t="n">
-        <v>6758296</v>
+        <v>6758227</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4001,7 +3996,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4011,7 +4006,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På stubbe med fem brandljud</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4250,10 +4250,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131448192</v>
+        <v>131440214</v>
       </c>
       <c r="B36" t="n">
-        <v>79868</v>
+        <v>79249</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4261,37 +4261,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>386439</v>
+        <v>386626</v>
       </c>
       <c r="R36" t="n">
-        <v>6758323</v>
+        <v>6758448</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4318,24 +4318,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På silverlåga</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4350,22 +4335,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131440214</v>
+        <v>131448192</v>
       </c>
       <c r="B37" t="n">
-        <v>79249</v>
+        <v>79868</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4373,37 +4358,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>386626</v>
+        <v>386439</v>
       </c>
       <c r="R37" t="n">
-        <v>6758448</v>
+        <v>6758323</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4430,9 +4415,24 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På silverlåga</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4447,60 +4447,60 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131448258</v>
+        <v>131440158</v>
       </c>
       <c r="B38" t="n">
-        <v>79273</v>
+        <v>79868</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>386544</v>
+        <v>386641</v>
       </c>
       <c r="R38" t="n">
-        <v>6758480</v>
+        <v>6758465</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4527,19 +4527,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>13:55</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4554,44 +4544,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131448250</v>
+        <v>131448258</v>
       </c>
       <c r="B39" t="n">
-        <v>79868</v>
+        <v>79273</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4601,10 +4591,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>386540</v>
+        <v>386544</v>
       </c>
       <c r="R39" t="n">
-        <v>6758409</v>
+        <v>6758480</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4636,7 +4626,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4646,7 +4636,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4673,50 +4663,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131448248</v>
+        <v>131448250</v>
       </c>
       <c r="B40" t="n">
-        <v>57076</v>
+        <v>79868</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>386531</v>
+        <v>386540</v>
       </c>
       <c r="R40" t="n">
-        <v>6758378</v>
+        <v>6758409</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4748,7 +4733,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4758,7 +4743,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4785,10 +4770,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131440158</v>
+        <v>131448247</v>
       </c>
       <c r="B41" t="n">
-        <v>79868</v>
+        <v>79249</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4796,37 +4781,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>386641</v>
+        <v>386499</v>
       </c>
       <c r="R41" t="n">
-        <v>6758465</v>
+        <v>6758353</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4853,9 +4838,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4870,50 +4865,50 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131448253</v>
+        <v>131448199</v>
       </c>
       <c r="B42" t="n">
-        <v>57076</v>
+        <v>57887</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4922,10 +4917,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>386556</v>
+        <v>386260</v>
       </c>
       <c r="R42" t="n">
-        <v>6758446</v>
+        <v>6758238</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4957,7 +4952,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4967,7 +4962,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5101,53 +5101,56 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131448199</v>
+        <v>131440177</v>
       </c>
       <c r="B44" t="n">
-        <v>57887</v>
+        <v>57076</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>386260</v>
+        <v>386568</v>
       </c>
       <c r="R44" t="n">
-        <v>6758238</v>
+        <v>6758395</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5174,24 +5177,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5206,57 +5194,62 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131448247</v>
+        <v>131448253</v>
       </c>
       <c r="B45" t="n">
-        <v>79249</v>
+        <v>57076</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>386499</v>
+        <v>386556</v>
       </c>
       <c r="R45" t="n">
-        <v>6758353</v>
+        <v>6758446</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5288,7 +5281,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5298,7 +5291,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5325,56 +5318,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131440177</v>
+        <v>131448246</v>
       </c>
       <c r="B46" t="n">
-        <v>57076</v>
+        <v>79249</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>386568</v>
+        <v>386523</v>
       </c>
       <c r="R46" t="n">
-        <v>6758395</v>
+        <v>6758350</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5401,9 +5386,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5418,44 +5413,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131440199</v>
+        <v>131440160</v>
       </c>
       <c r="B47" t="n">
-        <v>79273</v>
+        <v>79868</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5465,10 +5460,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>386562</v>
+        <v>386635</v>
       </c>
       <c r="R47" t="n">
-        <v>6758346</v>
+        <v>6758461</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5527,32 +5522,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131440160</v>
+        <v>131440199</v>
       </c>
       <c r="B48" t="n">
-        <v>79868</v>
+        <v>79273</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5562,10 +5557,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>386635</v>
+        <v>386562</v>
       </c>
       <c r="R48" t="n">
-        <v>6758461</v>
+        <v>6758346</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5624,10 +5619,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131448246</v>
+        <v>131440164</v>
       </c>
       <c r="B49" t="n">
-        <v>79249</v>
+        <v>79868</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5635,37 +5630,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>386523</v>
+        <v>386578</v>
       </c>
       <c r="R49" t="n">
-        <v>6758350</v>
+        <v>6758384</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5692,19 +5687,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>14:02</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5719,22 +5704,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131440164</v>
+        <v>131448200</v>
       </c>
       <c r="B50" t="n">
-        <v>79868</v>
+        <v>79249</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5742,37 +5727,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>386578</v>
+        <v>386260</v>
       </c>
       <c r="R50" t="n">
-        <v>6758384</v>
+        <v>6758238</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5799,9 +5784,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5816,19 +5811,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131440159</v>
+        <v>131440162</v>
       </c>
       <c r="B51" t="n">
         <v>79868</v>
@@ -5863,10 +5858,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>386631</v>
+        <v>386621</v>
       </c>
       <c r="R51" t="n">
-        <v>6758450</v>
+        <v>6758445</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -5925,56 +5920,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131440178</v>
+        <v>131448245</v>
       </c>
       <c r="B52" t="n">
-        <v>57076</v>
+        <v>79249</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>386543</v>
+        <v>386509</v>
       </c>
       <c r="R52" t="n">
-        <v>6758407</v>
+        <v>6758270</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6001,9 +5988,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6018,19 +6015,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131440162</v>
+        <v>131440159</v>
       </c>
       <c r="B53" t="n">
         <v>79868</v>
@@ -6065,10 +6062,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>386621</v>
+        <v>386631</v>
       </c>
       <c r="R53" t="n">
-        <v>6758445</v>
+        <v>6758450</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6127,45 +6124,50 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131448200</v>
+        <v>131448235</v>
       </c>
       <c r="B54" t="n">
-        <v>79249</v>
+        <v>57076</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>386260</v>
+        <v>386484</v>
       </c>
       <c r="R54" t="n">
-        <v>6758238</v>
+        <v>6758183</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6197,7 +6199,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6207,7 +6209,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6234,48 +6236,56 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131448245</v>
+        <v>131440178</v>
       </c>
       <c r="B55" t="n">
-        <v>79249</v>
+        <v>57076</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>386509</v>
+        <v>386543</v>
       </c>
       <c r="R55" t="n">
-        <v>6758270</v>
+        <v>6758407</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6302,19 +6312,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>14:07</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>14:07</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6329,65 +6329,60 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131448235</v>
+        <v>131440212</v>
       </c>
       <c r="B56" t="n">
-        <v>57076</v>
+        <v>79249</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>386484</v>
+        <v>386638</v>
       </c>
       <c r="R56" t="n">
-        <v>6758183</v>
+        <v>6758463</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6414,19 +6409,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>14:11</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>14:11</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6441,12 +6426,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6647,10 +6632,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131440212</v>
+        <v>131440209</v>
       </c>
       <c r="B59" t="n">
-        <v>79249</v>
+        <v>79007</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6658,21 +6643,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6682,10 +6667,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>386638</v>
+        <v>386659</v>
       </c>
       <c r="R59" t="n">
-        <v>6758463</v>
+        <v>6758445</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -6744,48 +6729,53 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131440209</v>
+        <v>131448240</v>
       </c>
       <c r="B60" t="n">
-        <v>79007</v>
+        <v>57076</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>386659</v>
+        <v>386487</v>
       </c>
       <c r="R60" t="n">
-        <v>6758445</v>
+        <v>6758237</v>
       </c>
       <c r="S60" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6812,9 +6802,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6829,19 +6829,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131448240</v>
+        <v>131448198</v>
       </c>
       <c r="B61" t="n">
         <v>57076</v>
@@ -6881,10 +6881,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>386487</v>
+        <v>386265</v>
       </c>
       <c r="R61" t="n">
-        <v>6758237</v>
+        <v>6758254</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6916,7 +6916,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6953,7 +6953,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131448198</v>
+        <v>131448248</v>
       </c>
       <c r="B62" t="n">
         <v>57076</v>
@@ -6993,10 +6993,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>386265</v>
+        <v>386531</v>
       </c>
       <c r="R62" t="n">
-        <v>6758254</v>
+        <v>6758378</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7028,7 +7028,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7038,7 +7038,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD62" t="b">

--- a/artfynd/A 6170-2026 artfynd.xlsx
+++ b/artfynd/A 6170-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131440157</v>
       </c>
       <c r="B2" t="n">
-        <v>79868</v>
+        <v>79869</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>131440202</v>
       </c>
       <c r="B3" t="n">
-        <v>79273</v>
+        <v>79274</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,45 +869,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131448241</v>
+        <v>131448191</v>
       </c>
       <c r="B4" t="n">
-        <v>79249</v>
+        <v>57076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>386485</v>
+        <v>386461</v>
       </c>
       <c r="R4" t="n">
-        <v>6758235</v>
+        <v>6758323</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -939,7 +944,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -949,7 +954,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,50 +981,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131448191</v>
+        <v>131448241</v>
       </c>
       <c r="B5" t="n">
-        <v>57076</v>
+        <v>79250</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>386461</v>
+        <v>386485</v>
       </c>
       <c r="R5" t="n">
-        <v>6758323</v>
+        <v>6758235</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,7 +1091,7 @@
         <v>131448256</v>
       </c>
       <c r="B6" t="n">
-        <v>78915</v>
+        <v>78916</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>131440198</v>
       </c>
       <c r="B7" t="n">
-        <v>79273</v>
+        <v>79274</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>131440208</v>
       </c>
       <c r="B8" t="n">
-        <v>79007</v>
+        <v>79008</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>131440154</v>
       </c>
       <c r="B10" t="n">
-        <v>79868</v>
+        <v>79869</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>131440201</v>
       </c>
       <c r="B11" t="n">
-        <v>79273</v>
+        <v>79274</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1905,10 +1905,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131448193</v>
+        <v>131440203</v>
       </c>
       <c r="B14" t="n">
-        <v>57076</v>
+        <v>79274</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1916,42 +1916,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>6434</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>386439</v>
+        <v>386523</v>
       </c>
       <c r="R14" t="n">
-        <v>6758323</v>
+        <v>6758426</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1978,19 +1973,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>14:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2005,65 +1990,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131448196</v>
+        <v>131440155</v>
       </c>
       <c r="B15" t="n">
-        <v>57076</v>
+        <v>79869</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>386393</v>
+        <v>386674</v>
       </c>
       <c r="R15" t="n">
-        <v>6758306</v>
+        <v>6758410</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2090,19 +2070,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2117,12 +2087,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2234,10 +2204,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131440203</v>
+        <v>131448193</v>
       </c>
       <c r="B17" t="n">
-        <v>79273</v>
+        <v>57076</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2245,37 +2215,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6434</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>386523</v>
+        <v>386439</v>
       </c>
       <c r="R17" t="n">
-        <v>6758426</v>
+        <v>6758323</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2302,9 +2277,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2319,60 +2304,65 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131440155</v>
+        <v>131448196</v>
       </c>
       <c r="B18" t="n">
-        <v>79868</v>
+        <v>57076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>386674</v>
+        <v>386393</v>
       </c>
       <c r="R18" t="n">
-        <v>6758410</v>
+        <v>6758306</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2399,9 +2389,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2416,62 +2416,57 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131448252</v>
+        <v>131448243</v>
       </c>
       <c r="B19" t="n">
-        <v>57076</v>
+        <v>79250</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>386539</v>
+        <v>386504</v>
       </c>
       <c r="R19" t="n">
-        <v>6758424</v>
+        <v>6758247</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2503,7 +2498,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2513,7 +2508,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2540,7 +2535,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131448195</v>
+        <v>131448252</v>
       </c>
       <c r="B20" t="n">
         <v>57076</v>
@@ -2569,9 +2564,9 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2580,10 +2575,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>386371</v>
+        <v>386539</v>
       </c>
       <c r="R20" t="n">
-        <v>6758307</v>
+        <v>6758424</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2615,7 +2610,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2625,7 +2620,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2652,45 +2647,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131448243</v>
+        <v>131448195</v>
       </c>
       <c r="B21" t="n">
-        <v>79249</v>
+        <v>57076</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>386504</v>
+        <v>386371</v>
       </c>
       <c r="R21" t="n">
-        <v>6758247</v>
+        <v>6758307</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2762,7 +2762,7 @@
         <v>131448202</v>
       </c>
       <c r="B22" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>131440213</v>
       </c>
       <c r="B23" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2963,45 +2963,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131448203</v>
+        <v>131448233</v>
       </c>
       <c r="B24" t="n">
-        <v>79249</v>
+        <v>57076</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>386191</v>
+        <v>386438</v>
       </c>
       <c r="R24" t="n">
-        <v>6758252</v>
+        <v>6758131</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3033,7 +3038,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3043,7 +3048,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3070,50 +3075,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131448233</v>
+        <v>131448203</v>
       </c>
       <c r="B25" t="n">
-        <v>57076</v>
+        <v>79250</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>386438</v>
+        <v>386191</v>
       </c>
       <c r="R25" t="n">
-        <v>6758131</v>
+        <v>6758252</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3182,48 +3182,53 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131440153</v>
+        <v>131448249</v>
       </c>
       <c r="B26" t="n">
-        <v>79868</v>
+        <v>57076</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>386590</v>
+        <v>386523</v>
       </c>
       <c r="R26" t="n">
-        <v>6758339</v>
+        <v>6758378</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3250,9 +3255,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3267,65 +3282,60 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131448249</v>
+        <v>131440153</v>
       </c>
       <c r="B27" t="n">
-        <v>57076</v>
+        <v>79869</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>386523</v>
+        <v>386590</v>
       </c>
       <c r="R27" t="n">
-        <v>6758378</v>
+        <v>6758339</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3352,19 +3362,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>14:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3379,22 +3379,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131448234</v>
+        <v>131448242</v>
       </c>
       <c r="B28" t="n">
-        <v>79249</v>
+        <v>78916</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3402,21 +3402,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>386438</v>
+        <v>386479</v>
       </c>
       <c r="R28" t="n">
-        <v>6758131</v>
+        <v>6758227</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3461,7 +3461,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3471,7 +3471,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På stubbe med fem brandljud</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3501,7 +3506,7 @@
         <v>131448254</v>
       </c>
       <c r="B29" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3605,10 +3610,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131448255</v>
+        <v>131448234</v>
       </c>
       <c r="B30" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3640,10 +3645,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>386544</v>
+        <v>386438</v>
       </c>
       <c r="R30" t="n">
-        <v>6758480</v>
+        <v>6758131</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3675,7 +3680,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3685,7 +3690,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3712,10 +3717,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131448194</v>
+        <v>131448239</v>
       </c>
       <c r="B31" t="n">
-        <v>79249</v>
+        <v>79869</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3723,21 +3728,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3747,10 +3752,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>386442</v>
+        <v>386487</v>
       </c>
       <c r="R31" t="n">
-        <v>6758296</v>
+        <v>6758237</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3782,7 +3787,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3792,7 +3797,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3819,10 +3824,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131448239</v>
+        <v>131448255</v>
       </c>
       <c r="B32" t="n">
-        <v>79868</v>
+        <v>79250</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3830,21 +3835,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3854,10 +3859,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>386487</v>
+        <v>386544</v>
       </c>
       <c r="R32" t="n">
-        <v>6758237</v>
+        <v>6758480</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3889,7 +3894,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3899,7 +3904,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3926,10 +3931,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131448242</v>
+        <v>131448194</v>
       </c>
       <c r="B33" t="n">
-        <v>78915</v>
+        <v>79250</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3937,21 +3942,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3961,10 +3966,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>386479</v>
+        <v>386442</v>
       </c>
       <c r="R33" t="n">
-        <v>6758227</v>
+        <v>6758296</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3996,7 +4001,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4006,12 +4011,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:09</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På stubbe med fem brandljud</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4146,7 +4146,7 @@
         <v>131448197</v>
       </c>
       <c r="B35" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4250,10 +4250,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131440214</v>
+        <v>131448192</v>
       </c>
       <c r="B36" t="n">
-        <v>79249</v>
+        <v>79869</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4261,37 +4261,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>386626</v>
+        <v>386439</v>
       </c>
       <c r="R36" t="n">
-        <v>6758448</v>
+        <v>6758323</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4318,9 +4318,24 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På silverlåga</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4335,22 +4350,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131448192</v>
+        <v>131440214</v>
       </c>
       <c r="B37" t="n">
-        <v>79868</v>
+        <v>79250</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4358,37 +4373,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>386439</v>
+        <v>386626</v>
       </c>
       <c r="R37" t="n">
-        <v>6758323</v>
+        <v>6758448</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4415,24 +4430,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På silverlåga</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4447,12 +4447,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4462,7 +4462,7 @@
         <v>131440158</v>
       </c>
       <c r="B38" t="n">
-        <v>79868</v>
+        <v>79869</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
         <v>131448258</v>
       </c>
       <c r="B39" t="n">
-        <v>79273</v>
+        <v>79274</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>131448250</v>
       </c>
       <c r="B40" t="n">
-        <v>79868</v>
+        <v>79869</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131448247</v>
+        <v>131448236</v>
       </c>
       <c r="B41" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4805,10 +4805,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>386499</v>
+        <v>386484</v>
       </c>
       <c r="R41" t="n">
-        <v>6758353</v>
+        <v>6758183</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4840,7 +4840,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4877,10 +4877,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131448199</v>
+        <v>131448247</v>
       </c>
       <c r="B42" t="n">
-        <v>57887</v>
+        <v>79250</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4888,39 +4888,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>386260</v>
+        <v>386499</v>
       </c>
       <c r="R42" t="n">
-        <v>6758238</v>
+        <v>6758353</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4952,7 +4947,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4962,12 +4957,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4994,48 +4984,56 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131448236</v>
+        <v>131440177</v>
       </c>
       <c r="B43" t="n">
-        <v>79249</v>
+        <v>57076</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>386484</v>
+        <v>386568</v>
       </c>
       <c r="R43" t="n">
-        <v>6758183</v>
+        <v>6758395</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5062,19 +5060,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>14:11</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>14:11</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5089,19 +5077,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131440177</v>
+        <v>131448253</v>
       </c>
       <c r="B44" t="n">
         <v>57076</v>
@@ -5130,27 +5118,24 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>386568</v>
+        <v>386556</v>
       </c>
       <c r="R44" t="n">
-        <v>6758395</v>
+        <v>6758446</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5177,9 +5162,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5194,50 +5189,50 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131448253</v>
+        <v>131448199</v>
       </c>
       <c r="B45" t="n">
-        <v>57076</v>
+        <v>57888</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5246,10 +5241,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>386556</v>
+        <v>386260</v>
       </c>
       <c r="R45" t="n">
-        <v>6758446</v>
+        <v>6758238</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5281,7 +5276,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5291,7 +5286,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5318,10 +5318,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131448246</v>
+        <v>131440160</v>
       </c>
       <c r="B46" t="n">
-        <v>79249</v>
+        <v>79869</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5329,37 +5329,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>386523</v>
+        <v>386635</v>
       </c>
       <c r="R46" t="n">
-        <v>6758350</v>
+        <v>6758461</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5386,19 +5386,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>14:02</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5413,22 +5403,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131440160</v>
+        <v>131448246</v>
       </c>
       <c r="B47" t="n">
-        <v>79868</v>
+        <v>79250</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5436,37 +5426,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>386635</v>
+        <v>386523</v>
       </c>
       <c r="R47" t="n">
-        <v>6758461</v>
+        <v>6758350</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5493,9 +5483,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5510,12 +5510,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5525,7 +5525,7 @@
         <v>131440199</v>
       </c>
       <c r="B48" t="n">
-        <v>79273</v>
+        <v>79274</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5622,7 +5622,7 @@
         <v>131440164</v>
       </c>
       <c r="B49" t="n">
-        <v>79868</v>
+        <v>79869</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5716,10 +5716,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131448200</v>
+        <v>131440162</v>
       </c>
       <c r="B50" t="n">
-        <v>79249</v>
+        <v>79869</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5727,37 +5727,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>386260</v>
+        <v>386621</v>
       </c>
       <c r="R50" t="n">
-        <v>6758238</v>
+        <v>6758445</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5784,19 +5784,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>14:42</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5811,22 +5801,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131440162</v>
+        <v>131448200</v>
       </c>
       <c r="B51" t="n">
-        <v>79868</v>
+        <v>79250</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5834,37 +5824,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>386621</v>
+        <v>386260</v>
       </c>
       <c r="R51" t="n">
-        <v>6758445</v>
+        <v>6758238</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5891,9 +5881,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5908,12 +5908,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -5923,7 +5923,7 @@
         <v>131448245</v>
       </c>
       <c r="B52" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         <v>131440159</v>
       </c>
       <c r="B53" t="n">
-        <v>79868</v>
+        <v>79869</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6341,10 +6341,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131440212</v>
+        <v>131440163</v>
       </c>
       <c r="B56" t="n">
-        <v>79249</v>
+        <v>79869</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6352,21 +6352,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6376,10 +6376,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>386638</v>
+        <v>386610</v>
       </c>
       <c r="R56" t="n">
-        <v>6758463</v>
+        <v>6758401</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6438,10 +6438,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131440163</v>
+        <v>131440156</v>
       </c>
       <c r="B57" t="n">
-        <v>79868</v>
+        <v>79869</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6473,10 +6473,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>386610</v>
+        <v>386665</v>
       </c>
       <c r="R57" t="n">
-        <v>6758401</v>
+        <v>6758445</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6535,10 +6535,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131440156</v>
+        <v>131440212</v>
       </c>
       <c r="B58" t="n">
-        <v>79868</v>
+        <v>79250</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6546,21 +6546,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6570,10 +6570,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>386665</v>
+        <v>386638</v>
       </c>
       <c r="R58" t="n">
-        <v>6758445</v>
+        <v>6758463</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -6635,7 +6635,7 @@
         <v>131440209</v>
       </c>
       <c r="B59" t="n">
-        <v>79007</v>
+        <v>79008</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 6170-2026 artfynd.xlsx
+++ b/artfynd/A 6170-2026 artfynd.xlsx
@@ -1389,53 +1389,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131448251</v>
+        <v>131440154</v>
       </c>
       <c r="B9" t="n">
-        <v>57076</v>
+        <v>79869</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>386544</v>
+        <v>386638</v>
       </c>
       <c r="R9" t="n">
-        <v>6758394</v>
+        <v>6758376</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1462,19 +1457,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>13:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1489,60 +1474,65 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131440154</v>
+        <v>131448251</v>
       </c>
       <c r="B10" t="n">
-        <v>79869</v>
+        <v>57076</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>386638</v>
+        <v>386544</v>
       </c>
       <c r="R10" t="n">
-        <v>6758376</v>
+        <v>6758394</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1569,9 +1559,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1586,12 +1586,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -2099,7 +2099,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131440176</v>
+        <v>131448193</v>
       </c>
       <c r="B16" t="n">
         <v>57076</v>
@@ -2128,27 +2128,24 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>386587</v>
+        <v>386439</v>
       </c>
       <c r="R16" t="n">
-        <v>6758386</v>
+        <v>6758323</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2175,9 +2172,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2192,19 +2199,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131448193</v>
+        <v>131448196</v>
       </c>
       <c r="B17" t="n">
         <v>57076</v>
@@ -2244,10 +2251,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>386439</v>
+        <v>386393</v>
       </c>
       <c r="R17" t="n">
-        <v>6758323</v>
+        <v>6758306</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2279,7 +2286,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2289,7 +2296,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2316,7 +2323,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131448196</v>
+        <v>131440176</v>
       </c>
       <c r="B18" t="n">
         <v>57076</v>
@@ -2345,24 +2352,27 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>386393</v>
+        <v>386587</v>
       </c>
       <c r="R18" t="n">
-        <v>6758306</v>
+        <v>6758386</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2389,19 +2399,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>14:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2416,12 +2416,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2963,50 +2963,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131448233</v>
+        <v>131448203</v>
       </c>
       <c r="B24" t="n">
-        <v>57076</v>
+        <v>79250</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>386438</v>
+        <v>386191</v>
       </c>
       <c r="R24" t="n">
-        <v>6758131</v>
+        <v>6758252</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3038,7 +3033,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3048,7 +3043,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3075,45 +3070,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131448203</v>
+        <v>131448233</v>
       </c>
       <c r="B25" t="n">
-        <v>79250</v>
+        <v>57076</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>386191</v>
+        <v>386438</v>
       </c>
       <c r="R25" t="n">
-        <v>6758252</v>
+        <v>6758131</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3182,53 +3182,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131448249</v>
+        <v>131440153</v>
       </c>
       <c r="B26" t="n">
-        <v>57076</v>
+        <v>79869</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>386523</v>
+        <v>386590</v>
       </c>
       <c r="R26" t="n">
-        <v>6758378</v>
+        <v>6758339</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3255,19 +3250,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3282,60 +3267,65 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131440153</v>
+        <v>131448249</v>
       </c>
       <c r="B27" t="n">
-        <v>79869</v>
+        <v>57076</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>386590</v>
+        <v>386523</v>
       </c>
       <c r="R27" t="n">
-        <v>6758339</v>
+        <v>6758378</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3362,9 +3352,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3379,22 +3379,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131448242</v>
+        <v>131448194</v>
       </c>
       <c r="B28" t="n">
-        <v>78916</v>
+        <v>79250</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3402,21 +3402,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>386479</v>
+        <v>386442</v>
       </c>
       <c r="R28" t="n">
-        <v>6758227</v>
+        <v>6758296</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3461,7 +3461,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3471,12 +3471,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:09</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På stubbe med fem brandljud</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3503,10 +3498,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131448254</v>
+        <v>131448242</v>
       </c>
       <c r="B29" t="n">
-        <v>79250</v>
+        <v>78916</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3514,21 +3509,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3538,10 +3533,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>386541</v>
+        <v>386479</v>
       </c>
       <c r="R29" t="n">
-        <v>6758426</v>
+        <v>6758227</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3573,7 +3568,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3583,7 +3578,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På stubbe med fem brandljud</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3610,7 +3610,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131448234</v>
+        <v>131448254</v>
       </c>
       <c r="B30" t="n">
         <v>79250</v>
@@ -3645,10 +3645,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>386438</v>
+        <v>386541</v>
       </c>
       <c r="R30" t="n">
-        <v>6758131</v>
+        <v>6758426</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3717,10 +3717,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131448239</v>
+        <v>131448234</v>
       </c>
       <c r="B31" t="n">
-        <v>79869</v>
+        <v>79250</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3728,21 +3728,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3752,10 +3752,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>386487</v>
+        <v>386438</v>
       </c>
       <c r="R31" t="n">
-        <v>6758237</v>
+        <v>6758131</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3824,10 +3824,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131448255</v>
+        <v>131448239</v>
       </c>
       <c r="B32" t="n">
-        <v>79250</v>
+        <v>79869</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3835,21 +3835,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3859,10 +3859,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>386544</v>
+        <v>386487</v>
       </c>
       <c r="R32" t="n">
-        <v>6758480</v>
+        <v>6758237</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3931,7 +3931,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131448194</v>
+        <v>131448255</v>
       </c>
       <c r="B33" t="n">
         <v>79250</v>
@@ -3966,10 +3966,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>386442</v>
+        <v>386544</v>
       </c>
       <c r="R33" t="n">
-        <v>6758296</v>
+        <v>6758480</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4143,10 +4143,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131448197</v>
+        <v>131448192</v>
       </c>
       <c r="B35" t="n">
-        <v>79250</v>
+        <v>79869</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4154,21 +4154,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4178,10 +4178,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>386313</v>
+        <v>386439</v>
       </c>
       <c r="R35" t="n">
-        <v>6758273</v>
+        <v>6758323</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4213,7 +4213,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4223,7 +4223,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På silverlåga</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4250,10 +4255,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131448192</v>
+        <v>131448197</v>
       </c>
       <c r="B36" t="n">
-        <v>79869</v>
+        <v>79250</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4261,21 +4266,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4285,10 +4290,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>386439</v>
+        <v>386313</v>
       </c>
       <c r="R36" t="n">
-        <v>6758323</v>
+        <v>6758273</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4320,7 +4325,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4330,12 +4335,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På silverlåga</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5716,48 +5716,53 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131440162</v>
+        <v>131448235</v>
       </c>
       <c r="B50" t="n">
-        <v>79869</v>
+        <v>57076</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>386621</v>
+        <v>386484</v>
       </c>
       <c r="R50" t="n">
-        <v>6758445</v>
+        <v>6758183</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5784,9 +5789,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5801,60 +5816,68 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131448200</v>
+        <v>131440178</v>
       </c>
       <c r="B51" t="n">
-        <v>79250</v>
+        <v>57076</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>386260</v>
+        <v>386543</v>
       </c>
       <c r="R51" t="n">
-        <v>6758238</v>
+        <v>6758407</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5881,19 +5904,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>14:42</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5908,22 +5921,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131448245</v>
+        <v>131440162</v>
       </c>
       <c r="B52" t="n">
-        <v>79250</v>
+        <v>79869</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5931,37 +5944,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>386509</v>
+        <v>386621</v>
       </c>
       <c r="R52" t="n">
-        <v>6758270</v>
+        <v>6758445</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5988,19 +6001,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>14:07</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>14:07</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6015,22 +6018,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131440159</v>
+        <v>131448200</v>
       </c>
       <c r="B53" t="n">
-        <v>79869</v>
+        <v>79250</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6038,37 +6041,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>386631</v>
+        <v>386260</v>
       </c>
       <c r="R53" t="n">
-        <v>6758450</v>
+        <v>6758238</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6095,9 +6098,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6112,62 +6125,57 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131448235</v>
+        <v>131448245</v>
       </c>
       <c r="B54" t="n">
-        <v>57076</v>
+        <v>79250</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>386484</v>
+        <v>386509</v>
       </c>
       <c r="R54" t="n">
-        <v>6758183</v>
+        <v>6758270</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6199,7 +6207,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6209,7 +6217,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6236,53 +6244,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131440178</v>
+        <v>131440159</v>
       </c>
       <c r="B55" t="n">
-        <v>57076</v>
+        <v>79869</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>386543</v>
+        <v>386631</v>
       </c>
       <c r="R55" t="n">
-        <v>6758407</v>
+        <v>6758450</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>

--- a/artfynd/A 6170-2026 artfynd.xlsx
+++ b/artfynd/A 6170-2026 artfynd.xlsx
@@ -869,50 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131448191</v>
+        <v>131448241</v>
       </c>
       <c r="B4" t="n">
-        <v>57076</v>
+        <v>79250</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>386461</v>
+        <v>386485</v>
       </c>
       <c r="R4" t="n">
-        <v>6758323</v>
+        <v>6758235</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -944,7 +939,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -954,7 +949,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,45 +976,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131448241</v>
+        <v>131448191</v>
       </c>
       <c r="B5" t="n">
-        <v>79250</v>
+        <v>57076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>386485</v>
+        <v>386461</v>
       </c>
       <c r="R5" t="n">
-        <v>6758235</v>
+        <v>6758323</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,48 +1088,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131448256</v>
+        <v>131440198</v>
       </c>
       <c r="B6" t="n">
-        <v>78916</v>
+        <v>79274</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6434</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>386545</v>
+        <v>386498</v>
       </c>
       <c r="R6" t="n">
-        <v>6758481</v>
+        <v>6758310</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1156,19 +1156,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,44 +1173,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131440198</v>
+        <v>131440208</v>
       </c>
       <c r="B7" t="n">
-        <v>79274</v>
+        <v>79008</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6434</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>386498</v>
+        <v>386669</v>
       </c>
       <c r="R7" t="n">
-        <v>6758310</v>
+        <v>6758449</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1292,10 +1282,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131440208</v>
+        <v>131448256</v>
       </c>
       <c r="B8" t="n">
-        <v>79008</v>
+        <v>78916</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,37 +1293,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>386669</v>
+        <v>386545</v>
       </c>
       <c r="R8" t="n">
-        <v>6758449</v>
+        <v>6758481</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1360,9 +1350,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1377,12 +1377,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -2428,45 +2428,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131448243</v>
+        <v>131448252</v>
       </c>
       <c r="B19" t="n">
-        <v>79250</v>
+        <v>57076</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>386504</v>
+        <v>386539</v>
       </c>
       <c r="R19" t="n">
-        <v>6758247</v>
+        <v>6758424</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2498,7 +2503,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2508,7 +2513,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2535,7 +2540,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131448252</v>
+        <v>131448195</v>
       </c>
       <c r="B20" t="n">
         <v>57076</v>
@@ -2564,9 +2569,9 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>hona</t>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2575,10 +2580,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>386539</v>
+        <v>386371</v>
       </c>
       <c r="R20" t="n">
-        <v>6758424</v>
+        <v>6758307</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2610,7 +2615,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2620,7 +2625,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2647,50 +2652,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131448195</v>
+        <v>131448243</v>
       </c>
       <c r="B21" t="n">
-        <v>57076</v>
+        <v>79250</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>386371</v>
+        <v>386504</v>
       </c>
       <c r="R21" t="n">
-        <v>6758307</v>
+        <v>6758247</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -4143,10 +4143,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131448192</v>
+        <v>131448197</v>
       </c>
       <c r="B35" t="n">
-        <v>79869</v>
+        <v>79250</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4154,21 +4154,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4178,10 +4178,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>386439</v>
+        <v>386313</v>
       </c>
       <c r="R35" t="n">
-        <v>6758323</v>
+        <v>6758273</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4213,7 +4213,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4223,12 +4223,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På silverlåga</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4255,10 +4250,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131448197</v>
+        <v>131448192</v>
       </c>
       <c r="B36" t="n">
-        <v>79250</v>
+        <v>79869</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4266,21 +4261,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4290,10 +4285,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>386313</v>
+        <v>386439</v>
       </c>
       <c r="R36" t="n">
-        <v>6758273</v>
+        <v>6758323</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4325,7 +4320,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4335,7 +4330,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På silverlåga</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5318,32 +5318,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131440160</v>
+        <v>131440199</v>
       </c>
       <c r="B46" t="n">
-        <v>79869</v>
+        <v>79274</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5353,10 +5353,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>386635</v>
+        <v>386562</v>
       </c>
       <c r="R46" t="n">
-        <v>6758461</v>
+        <v>6758346</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5415,10 +5415,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131448246</v>
+        <v>131440160</v>
       </c>
       <c r="B47" t="n">
-        <v>79250</v>
+        <v>79869</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5426,37 +5426,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>386523</v>
+        <v>386635</v>
       </c>
       <c r="R47" t="n">
-        <v>6758350</v>
+        <v>6758461</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5483,19 +5483,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>14:02</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5510,60 +5500,60 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131440199</v>
+        <v>131448246</v>
       </c>
       <c r="B48" t="n">
-        <v>79274</v>
+        <v>79250</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>386562</v>
+        <v>386523</v>
       </c>
       <c r="R48" t="n">
-        <v>6758346</v>
+        <v>6758350</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5590,9 +5580,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5607,12 +5607,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>

--- a/artfynd/A 6170-2026 artfynd.xlsx
+++ b/artfynd/A 6170-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131440157</v>
       </c>
       <c r="B2" t="n">
-        <v>79869</v>
+        <v>79872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>131440202</v>
       </c>
       <c r="B3" t="n">
-        <v>79274</v>
+        <v>79277</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>131448241</v>
       </c>
       <c r="B4" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>131448191</v>
       </c>
       <c r="B5" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,32 +1088,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131440198</v>
+        <v>131440208</v>
       </c>
       <c r="B6" t="n">
-        <v>79274</v>
+        <v>79011</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6434</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>386498</v>
+        <v>386669</v>
       </c>
       <c r="R6" t="n">
-        <v>6758310</v>
+        <v>6758449</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131440208</v>
+        <v>131448256</v>
       </c>
       <c r="B7" t="n">
-        <v>79008</v>
+        <v>78919</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,37 +1196,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>386669</v>
+        <v>386545</v>
       </c>
       <c r="R7" t="n">
-        <v>6758449</v>
+        <v>6758481</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1253,9 +1253,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1270,60 +1280,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131448256</v>
+        <v>131440198</v>
       </c>
       <c r="B8" t="n">
-        <v>78916</v>
+        <v>79277</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>6434</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>386545</v>
+        <v>386498</v>
       </c>
       <c r="R8" t="n">
-        <v>6758481</v>
+        <v>6758310</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1350,19 +1360,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:56</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1377,12 +1377,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1392,7 +1392,7 @@
         <v>131440154</v>
       </c>
       <c r="B9" t="n">
-        <v>79869</v>
+        <v>79872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>131448251</v>
       </c>
       <c r="B10" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>131440201</v>
       </c>
       <c r="B11" t="n">
-        <v>79274</v>
+        <v>79277</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>131440175</v>
       </c>
       <c r="B12" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>131440173</v>
       </c>
       <c r="B13" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1905,10 +1905,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131440203</v>
+        <v>131448193</v>
       </c>
       <c r="B14" t="n">
-        <v>79274</v>
+        <v>57079</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1916,37 +1916,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6434</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>386523</v>
+        <v>386439</v>
       </c>
       <c r="R14" t="n">
-        <v>6758426</v>
+        <v>6758323</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1973,9 +1978,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1990,60 +2005,65 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131440155</v>
+        <v>131448196</v>
       </c>
       <c r="B15" t="n">
-        <v>79869</v>
+        <v>57079</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>386674</v>
+        <v>386393</v>
       </c>
       <c r="R15" t="n">
-        <v>6758410</v>
+        <v>6758306</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2070,9 +2090,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2087,22 +2117,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131448193</v>
+        <v>131440176</v>
       </c>
       <c r="B16" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2128,24 +2158,27 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>386439</v>
+        <v>386587</v>
       </c>
       <c r="R16" t="n">
-        <v>6758323</v>
+        <v>6758386</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2172,19 +2205,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>14:48</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2199,22 +2222,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131448196</v>
+        <v>131440203</v>
       </c>
       <c r="B17" t="n">
-        <v>57076</v>
+        <v>79277</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2222,42 +2245,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6434</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>386393</v>
+        <v>386523</v>
       </c>
       <c r="R17" t="n">
-        <v>6758306</v>
+        <v>6758426</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2284,19 +2302,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>14:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2311,65 +2319,57 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131440176</v>
+        <v>131440155</v>
       </c>
       <c r="B18" t="n">
-        <v>57076</v>
+        <v>79872</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>386587</v>
+        <v>386674</v>
       </c>
       <c r="R18" t="n">
-        <v>6758386</v>
+        <v>6758410</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2428,50 +2428,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131448252</v>
+        <v>131448243</v>
       </c>
       <c r="B19" t="n">
-        <v>57076</v>
+        <v>79253</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>386539</v>
+        <v>386504</v>
       </c>
       <c r="R19" t="n">
-        <v>6758424</v>
+        <v>6758247</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2503,7 +2498,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2513,7 +2508,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2540,10 +2535,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131448195</v>
+        <v>131448252</v>
       </c>
       <c r="B20" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2569,9 +2564,9 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2580,10 +2575,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>386371</v>
+        <v>386539</v>
       </c>
       <c r="R20" t="n">
-        <v>6758307</v>
+        <v>6758424</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2615,7 +2610,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2625,7 +2620,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2652,45 +2647,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131448243</v>
+        <v>131448195</v>
       </c>
       <c r="B21" t="n">
-        <v>79250</v>
+        <v>57079</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>386504</v>
+        <v>386371</v>
       </c>
       <c r="R21" t="n">
-        <v>6758247</v>
+        <v>6758307</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2762,7 +2762,7 @@
         <v>131448202</v>
       </c>
       <c r="B22" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>131440213</v>
       </c>
       <c r="B23" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2963,45 +2963,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131448203</v>
+        <v>131448233</v>
       </c>
       <c r="B24" t="n">
-        <v>79250</v>
+        <v>57079</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>386191</v>
+        <v>386438</v>
       </c>
       <c r="R24" t="n">
-        <v>6758252</v>
+        <v>6758131</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3033,7 +3038,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3043,7 +3048,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3070,50 +3075,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131448233</v>
+        <v>131448203</v>
       </c>
       <c r="B25" t="n">
-        <v>57076</v>
+        <v>79253</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>386438</v>
+        <v>386191</v>
       </c>
       <c r="R25" t="n">
-        <v>6758131</v>
+        <v>6758252</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3185,7 +3185,7 @@
         <v>131440153</v>
       </c>
       <c r="B26" t="n">
-        <v>79869</v>
+        <v>79872</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>131448249</v>
       </c>
       <c r="B27" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3391,10 +3391,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131448194</v>
+        <v>131448242</v>
       </c>
       <c r="B28" t="n">
-        <v>79250</v>
+        <v>78919</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3402,21 +3402,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>386442</v>
+        <v>386479</v>
       </c>
       <c r="R28" t="n">
-        <v>6758296</v>
+        <v>6758227</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3461,7 +3461,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3471,7 +3471,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På stubbe med fem brandljud</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3498,10 +3503,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131448242</v>
+        <v>131448254</v>
       </c>
       <c r="B29" t="n">
-        <v>78916</v>
+        <v>79253</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3509,21 +3514,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3533,10 +3538,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>386479</v>
+        <v>386541</v>
       </c>
       <c r="R29" t="n">
-        <v>6758227</v>
+        <v>6758426</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3568,7 +3573,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3578,12 +3583,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:09</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På stubbe med fem brandljud</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3610,10 +3610,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131448254</v>
+        <v>131448234</v>
       </c>
       <c r="B30" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3645,10 +3645,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>386541</v>
+        <v>386438</v>
       </c>
       <c r="R30" t="n">
-        <v>6758426</v>
+        <v>6758131</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3717,10 +3717,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131448234</v>
+        <v>131448239</v>
       </c>
       <c r="B31" t="n">
-        <v>79250</v>
+        <v>79872</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3728,21 +3728,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3752,10 +3752,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>386438</v>
+        <v>386487</v>
       </c>
       <c r="R31" t="n">
-        <v>6758131</v>
+        <v>6758237</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3824,10 +3824,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131448239</v>
+        <v>131448255</v>
       </c>
       <c r="B32" t="n">
-        <v>79869</v>
+        <v>79253</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3835,21 +3835,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3859,10 +3859,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>386487</v>
+        <v>386544</v>
       </c>
       <c r="R32" t="n">
-        <v>6758237</v>
+        <v>6758480</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3931,10 +3931,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131448255</v>
+        <v>131448194</v>
       </c>
       <c r="B33" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3966,10 +3966,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>386544</v>
+        <v>386442</v>
       </c>
       <c r="R33" t="n">
-        <v>6758480</v>
+        <v>6758296</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4041,7 +4041,7 @@
         <v>131440174</v>
       </c>
       <c r="B34" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>131448197</v>
       </c>
       <c r="B35" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>131448192</v>
       </c>
       <c r="B36" t="n">
-        <v>79869</v>
+        <v>79872</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         <v>131440214</v>
       </c>
       <c r="B37" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         <v>131440158</v>
       </c>
       <c r="B38" t="n">
-        <v>79869</v>
+        <v>79872</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
         <v>131448258</v>
       </c>
       <c r="B39" t="n">
-        <v>79274</v>
+        <v>79277</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>131448250</v>
       </c>
       <c r="B40" t="n">
-        <v>79869</v>
+        <v>79872</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4770,48 +4770,56 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131448236</v>
+        <v>131440177</v>
       </c>
       <c r="B41" t="n">
-        <v>79250</v>
+        <v>57079</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>386484</v>
+        <v>386568</v>
       </c>
       <c r="R41" t="n">
-        <v>6758183</v>
+        <v>6758395</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4838,19 +4846,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>14:11</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>14:11</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4865,57 +4863,62 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131448247</v>
+        <v>131448253</v>
       </c>
       <c r="B42" t="n">
-        <v>79250</v>
+        <v>57079</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>386499</v>
+        <v>386556</v>
       </c>
       <c r="R42" t="n">
-        <v>6758353</v>
+        <v>6758446</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4947,7 +4950,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4957,7 +4960,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4984,56 +4987,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131440177</v>
+        <v>131448236</v>
       </c>
       <c r="B43" t="n">
-        <v>57076</v>
+        <v>79253</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>386568</v>
+        <v>386484</v>
       </c>
       <c r="R43" t="n">
-        <v>6758395</v>
+        <v>6758183</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5060,9 +5055,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5077,62 +5082,57 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131448253</v>
+        <v>131448247</v>
       </c>
       <c r="B44" t="n">
-        <v>57076</v>
+        <v>79253</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>386556</v>
+        <v>386499</v>
       </c>
       <c r="R44" t="n">
-        <v>6758446</v>
+        <v>6758353</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5164,7 +5164,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5204,7 +5204,7 @@
         <v>131448199</v>
       </c>
       <c r="B45" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5318,32 +5318,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131440199</v>
+        <v>131440160</v>
       </c>
       <c r="B46" t="n">
-        <v>79274</v>
+        <v>79872</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5353,10 +5353,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>386562</v>
+        <v>386635</v>
       </c>
       <c r="R46" t="n">
-        <v>6758346</v>
+        <v>6758461</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5415,10 +5415,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131440160</v>
+        <v>131448246</v>
       </c>
       <c r="B47" t="n">
-        <v>79869</v>
+        <v>79253</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5426,37 +5426,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>386635</v>
+        <v>386523</v>
       </c>
       <c r="R47" t="n">
-        <v>6758461</v>
+        <v>6758350</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5483,9 +5483,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5500,60 +5510,60 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131448246</v>
+        <v>131440199</v>
       </c>
       <c r="B48" t="n">
-        <v>79250</v>
+        <v>79277</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>386523</v>
+        <v>386562</v>
       </c>
       <c r="R48" t="n">
-        <v>6758350</v>
+        <v>6758346</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5580,19 +5590,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>14:02</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5607,12 +5607,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5622,7 +5622,7 @@
         <v>131440164</v>
       </c>
       <c r="B49" t="n">
-        <v>79869</v>
+        <v>79872</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>131448235</v>
       </c>
       <c r="B50" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>131440178</v>
       </c>
       <c r="B51" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>131440162</v>
       </c>
       <c r="B52" t="n">
-        <v>79869</v>
+        <v>79872</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         <v>131448200</v>
       </c>
       <c r="B53" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         <v>131448245</v>
       </c>
       <c r="B54" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         <v>131440159</v>
       </c>
       <c r="B55" t="n">
-        <v>79869</v>
+        <v>79872</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>131440163</v>
       </c>
       <c r="B56" t="n">
-        <v>79869</v>
+        <v>79872</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>131440156</v>
       </c>
       <c r="B57" t="n">
-        <v>79869</v>
+        <v>79872</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>131440212</v>
       </c>
       <c r="B58" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6635,7 +6635,7 @@
         <v>131440209</v>
       </c>
       <c r="B59" t="n">
-        <v>79008</v>
+        <v>79011</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>131448240</v>
       </c>
       <c r="B60" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>131448198</v>
       </c>
       <c r="B61" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         <v>131448248</v>
       </c>
       <c r="B62" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 6170-2026 artfynd.xlsx
+++ b/artfynd/A 6170-2026 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131440157</v>
+        <v>131440202</v>
       </c>
       <c r="B2" t="n">
-        <v>79872</v>
+        <v>79278</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>386666</v>
+        <v>386622</v>
       </c>
       <c r="R2" t="n">
-        <v>6758441</v>
+        <v>6758434</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131440202</v>
+        <v>131440157</v>
       </c>
       <c r="B3" t="n">
-        <v>79277</v>
+        <v>79873</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>386622</v>
+        <v>386666</v>
       </c>
       <c r="R3" t="n">
-        <v>6758434</v>
+        <v>6758441</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -872,7 +872,7 @@
         <v>131448241</v>
       </c>
       <c r="B4" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>131448191</v>
       </c>
       <c r="B5" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131440208</v>
+        <v>131448256</v>
       </c>
       <c r="B6" t="n">
-        <v>79011</v>
+        <v>78920</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,37 +1099,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>386669</v>
+        <v>386545</v>
       </c>
       <c r="R6" t="n">
-        <v>6758449</v>
+        <v>6758481</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1156,9 +1156,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,60 +1183,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131448256</v>
+        <v>131440198</v>
       </c>
       <c r="B7" t="n">
-        <v>78919</v>
+        <v>79278</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>6434</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>386545</v>
+        <v>386498</v>
       </c>
       <c r="R7" t="n">
-        <v>6758481</v>
+        <v>6758310</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1253,19 +1263,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1280,44 +1280,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131440198</v>
+        <v>131440208</v>
       </c>
       <c r="B8" t="n">
-        <v>79277</v>
+        <v>79012</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6434</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>386498</v>
+        <v>386669</v>
       </c>
       <c r="R8" t="n">
-        <v>6758310</v>
+        <v>6758449</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1392,7 +1392,7 @@
         <v>131440154</v>
       </c>
       <c r="B9" t="n">
-        <v>79872</v>
+        <v>79873</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>131448251</v>
       </c>
       <c r="B10" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>131440201</v>
       </c>
       <c r="B11" t="n">
-        <v>79277</v>
+        <v>79278</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>131440175</v>
       </c>
       <c r="B12" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>131440173</v>
       </c>
       <c r="B13" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1905,53 +1905,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131448193</v>
+        <v>131440155</v>
       </c>
       <c r="B14" t="n">
-        <v>57079</v>
+        <v>79873</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>386439</v>
+        <v>386674</v>
       </c>
       <c r="R14" t="n">
-        <v>6758323</v>
+        <v>6758410</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1978,19 +1973,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>14:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2005,22 +1990,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131448196</v>
+        <v>131440203</v>
       </c>
       <c r="B15" t="n">
-        <v>57079</v>
+        <v>79278</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2028,42 +2013,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6434</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>386393</v>
+        <v>386523</v>
       </c>
       <c r="R15" t="n">
-        <v>6758306</v>
+        <v>6758426</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2090,19 +2070,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2117,22 +2087,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131440176</v>
+        <v>131448193</v>
       </c>
       <c r="B16" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2158,27 +2128,24 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>386587</v>
+        <v>386439</v>
       </c>
       <c r="R16" t="n">
-        <v>6758386</v>
+        <v>6758323</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2205,9 +2172,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2222,22 +2199,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131440203</v>
+        <v>131448196</v>
       </c>
       <c r="B17" t="n">
-        <v>79277</v>
+        <v>57080</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2245,37 +2222,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6434</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>386523</v>
+        <v>386393</v>
       </c>
       <c r="R17" t="n">
-        <v>6758426</v>
+        <v>6758306</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2302,9 +2284,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2319,57 +2311,65 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131440155</v>
+        <v>131440176</v>
       </c>
       <c r="B18" t="n">
-        <v>79872</v>
+        <v>57080</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>386674</v>
+        <v>386587</v>
       </c>
       <c r="R18" t="n">
-        <v>6758410</v>
+        <v>6758386</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2431,7 +2431,7 @@
         <v>131448243</v>
       </c>
       <c r="B19" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>131448252</v>
       </c>
       <c r="B20" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>131448195</v>
       </c>
       <c r="B21" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>131448202</v>
       </c>
       <c r="B22" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>131440213</v>
       </c>
       <c r="B23" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2963,50 +2963,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131448233</v>
+        <v>131448203</v>
       </c>
       <c r="B24" t="n">
-        <v>57079</v>
+        <v>79254</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>386438</v>
+        <v>386191</v>
       </c>
       <c r="R24" t="n">
-        <v>6758131</v>
+        <v>6758252</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3038,7 +3033,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3048,7 +3043,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3075,45 +3070,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131448203</v>
+        <v>131448233</v>
       </c>
       <c r="B25" t="n">
-        <v>79253</v>
+        <v>57080</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>386191</v>
+        <v>386438</v>
       </c>
       <c r="R25" t="n">
-        <v>6758252</v>
+        <v>6758131</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3182,48 +3182,53 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131440153</v>
+        <v>131448249</v>
       </c>
       <c r="B26" t="n">
-        <v>79872</v>
+        <v>57080</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>386590</v>
+        <v>386523</v>
       </c>
       <c r="R26" t="n">
-        <v>6758339</v>
+        <v>6758378</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3250,9 +3255,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3267,65 +3282,60 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131448249</v>
+        <v>131440153</v>
       </c>
       <c r="B27" t="n">
-        <v>57079</v>
+        <v>79873</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>386523</v>
+        <v>386590</v>
       </c>
       <c r="R27" t="n">
-        <v>6758378</v>
+        <v>6758339</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3352,19 +3362,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>14:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3379,22 +3379,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131448242</v>
+        <v>131448239</v>
       </c>
       <c r="B28" t="n">
-        <v>78919</v>
+        <v>79873</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3402,21 +3402,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>386479</v>
+        <v>386487</v>
       </c>
       <c r="R28" t="n">
-        <v>6758227</v>
+        <v>6758237</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3472,11 +3472,6 @@
       <c r="AB28" t="inlineStr">
         <is>
           <t>14:09</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På stubbe med fem brandljud</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3503,10 +3498,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131448254</v>
+        <v>131448234</v>
       </c>
       <c r="B29" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3538,10 +3533,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>386541</v>
+        <v>386438</v>
       </c>
       <c r="R29" t="n">
-        <v>6758426</v>
+        <v>6758131</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3573,7 +3568,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3583,7 +3578,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3610,10 +3605,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131448234</v>
+        <v>131448194</v>
       </c>
       <c r="B30" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3645,10 +3640,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>386438</v>
+        <v>386442</v>
       </c>
       <c r="R30" t="n">
-        <v>6758131</v>
+        <v>6758296</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3680,7 +3675,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3690,7 +3685,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3717,10 +3712,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131448239</v>
+        <v>131448255</v>
       </c>
       <c r="B31" t="n">
-        <v>79872</v>
+        <v>79254</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3728,21 +3723,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3752,10 +3747,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>386487</v>
+        <v>386544</v>
       </c>
       <c r="R31" t="n">
-        <v>6758237</v>
+        <v>6758480</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3787,7 +3782,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3797,7 +3792,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3824,10 +3819,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131448255</v>
+        <v>131448254</v>
       </c>
       <c r="B32" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3859,10 +3854,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>386544</v>
+        <v>386541</v>
       </c>
       <c r="R32" t="n">
-        <v>6758480</v>
+        <v>6758426</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3894,7 +3889,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3904,7 +3899,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3931,48 +3926,56 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131448194</v>
+        <v>131440174</v>
       </c>
       <c r="B33" t="n">
-        <v>79253</v>
+        <v>57080</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>386442</v>
+        <v>386653</v>
       </c>
       <c r="R33" t="n">
-        <v>6758296</v>
+        <v>6758386</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3999,19 +4002,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>14:47</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4026,68 +4019,60 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131440174</v>
+        <v>131448242</v>
       </c>
       <c r="B34" t="n">
-        <v>57079</v>
+        <v>78920</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>386653</v>
+        <v>386479</v>
       </c>
       <c r="R34" t="n">
-        <v>6758386</v>
+        <v>6758227</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4114,9 +4099,24 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På stubbe med fem brandljud</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4131,22 +4131,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131448197</v>
+        <v>131440214</v>
       </c>
       <c r="B35" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4174,17 +4174,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>386313</v>
+        <v>386626</v>
       </c>
       <c r="R35" t="n">
-        <v>6758273</v>
+        <v>6758448</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4211,19 +4211,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>14:43</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4238,12 +4228,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4253,7 +4243,7 @@
         <v>131448192</v>
       </c>
       <c r="B36" t="n">
-        <v>79872</v>
+        <v>79873</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4362,10 +4352,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131440214</v>
+        <v>131448197</v>
       </c>
       <c r="B37" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4393,17 +4383,17 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>386626</v>
+        <v>386313</v>
       </c>
       <c r="R37" t="n">
-        <v>6758448</v>
+        <v>6758273</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4430,9 +4420,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4447,12 +4447,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4462,7 +4462,7 @@
         <v>131440158</v>
       </c>
       <c r="B38" t="n">
-        <v>79872</v>
+        <v>79873</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4556,32 +4556,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131448258</v>
+        <v>131448250</v>
       </c>
       <c r="B39" t="n">
-        <v>79277</v>
+        <v>79873</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>386544</v>
+        <v>386540</v>
       </c>
       <c r="R39" t="n">
-        <v>6758480</v>
+        <v>6758409</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4663,32 +4663,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131448250</v>
+        <v>131448258</v>
       </c>
       <c r="B40" t="n">
-        <v>79872</v>
+        <v>79278</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4698,10 +4698,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>386540</v>
+        <v>386544</v>
       </c>
       <c r="R40" t="n">
-        <v>6758409</v>
+        <v>6758480</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4733,7 +4733,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4743,7 +4743,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4770,56 +4770,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131440177</v>
+        <v>131448247</v>
       </c>
       <c r="B41" t="n">
-        <v>57079</v>
+        <v>79254</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>386568</v>
+        <v>386499</v>
       </c>
       <c r="R41" t="n">
-        <v>6758395</v>
+        <v>6758353</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4846,9 +4838,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4863,62 +4865,57 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131448253</v>
+        <v>131448236</v>
       </c>
       <c r="B42" t="n">
-        <v>57079</v>
+        <v>79254</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>386556</v>
+        <v>386484</v>
       </c>
       <c r="R42" t="n">
-        <v>6758446</v>
+        <v>6758183</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4950,7 +4947,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4960,7 +4957,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4987,10 +4984,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131448236</v>
+        <v>131448199</v>
       </c>
       <c r="B43" t="n">
-        <v>79253</v>
+        <v>57892</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4998,34 +4995,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>386484</v>
+        <v>386260</v>
       </c>
       <c r="R43" t="n">
-        <v>6758183</v>
+        <v>6758238</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5057,7 +5059,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5067,7 +5069,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5094,48 +5101,56 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131448247</v>
+        <v>131440177</v>
       </c>
       <c r="B44" t="n">
-        <v>79253</v>
+        <v>57080</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>386499</v>
+        <v>386568</v>
       </c>
       <c r="R44" t="n">
-        <v>6758353</v>
+        <v>6758395</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5162,19 +5177,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>14:02</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5189,50 +5194,50 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131448199</v>
+        <v>131448253</v>
       </c>
       <c r="B45" t="n">
-        <v>57891</v>
+        <v>57080</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5241,10 +5246,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>386260</v>
+        <v>386556</v>
       </c>
       <c r="R45" t="n">
-        <v>6758238</v>
+        <v>6758446</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5276,7 +5281,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5286,12 +5291,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5318,10 +5318,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131440160</v>
+        <v>131448246</v>
       </c>
       <c r="B46" t="n">
-        <v>79872</v>
+        <v>79254</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5329,37 +5329,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>386635</v>
+        <v>386523</v>
       </c>
       <c r="R46" t="n">
-        <v>6758461</v>
+        <v>6758350</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5386,9 +5386,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5403,60 +5413,60 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131448246</v>
+        <v>131440199</v>
       </c>
       <c r="B47" t="n">
-        <v>79253</v>
+        <v>79278</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>386523</v>
+        <v>386562</v>
       </c>
       <c r="R47" t="n">
-        <v>6758350</v>
+        <v>6758346</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5483,19 +5493,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>14:02</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5510,44 +5510,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131440199</v>
+        <v>131440160</v>
       </c>
       <c r="B48" t="n">
-        <v>79277</v>
+        <v>79873</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5557,10 +5557,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>386562</v>
+        <v>386635</v>
       </c>
       <c r="R48" t="n">
-        <v>6758346</v>
+        <v>6758461</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5622,7 +5622,7 @@
         <v>131440164</v>
       </c>
       <c r="B49" t="n">
-        <v>79872</v>
+        <v>79873</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5716,53 +5716,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131448235</v>
+        <v>131440159</v>
       </c>
       <c r="B50" t="n">
-        <v>57079</v>
+        <v>79873</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>386484</v>
+        <v>386631</v>
       </c>
       <c r="R50" t="n">
-        <v>6758183</v>
+        <v>6758450</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5789,19 +5784,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>14:11</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>14:11</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5816,68 +5801,60 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131440178</v>
+        <v>131448200</v>
       </c>
       <c r="B51" t="n">
-        <v>57079</v>
+        <v>79254</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>386543</v>
+        <v>386260</v>
       </c>
       <c r="R51" t="n">
-        <v>6758407</v>
+        <v>6758238</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5904,9 +5881,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5921,22 +5908,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131440162</v>
+        <v>131448245</v>
       </c>
       <c r="B52" t="n">
-        <v>79872</v>
+        <v>79254</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5944,37 +5931,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>386621</v>
+        <v>386509</v>
       </c>
       <c r="R52" t="n">
-        <v>6758445</v>
+        <v>6758270</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6001,9 +5988,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6018,22 +6015,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131448200</v>
+        <v>131440162</v>
       </c>
       <c r="B53" t="n">
-        <v>79253</v>
+        <v>79873</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6041,37 +6038,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>386260</v>
+        <v>386621</v>
       </c>
       <c r="R53" t="n">
-        <v>6758238</v>
+        <v>6758445</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6098,19 +6095,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>14:42</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6125,57 +6112,62 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131448245</v>
+        <v>131448235</v>
       </c>
       <c r="B54" t="n">
-        <v>79253</v>
+        <v>57080</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>386509</v>
+        <v>386484</v>
       </c>
       <c r="R54" t="n">
-        <v>6758270</v>
+        <v>6758183</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6207,7 +6199,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6217,7 +6209,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6244,45 +6236,53 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131440159</v>
+        <v>131440178</v>
       </c>
       <c r="B55" t="n">
-        <v>79872</v>
+        <v>57080</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>386631</v>
+        <v>386543</v>
       </c>
       <c r="R55" t="n">
-        <v>6758450</v>
+        <v>6758407</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6341,10 +6341,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131440163</v>
+        <v>131440209</v>
       </c>
       <c r="B56" t="n">
-        <v>79872</v>
+        <v>79012</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6352,21 +6352,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6376,10 +6376,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>386610</v>
+        <v>386659</v>
       </c>
       <c r="R56" t="n">
-        <v>6758401</v>
+        <v>6758445</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6438,10 +6438,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131440156</v>
+        <v>131440163</v>
       </c>
       <c r="B57" t="n">
-        <v>79872</v>
+        <v>79873</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6473,10 +6473,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>386665</v>
+        <v>386610</v>
       </c>
       <c r="R57" t="n">
-        <v>6758445</v>
+        <v>6758401</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6535,10 +6535,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131440212</v>
+        <v>131440156</v>
       </c>
       <c r="B58" t="n">
-        <v>79253</v>
+        <v>79873</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6546,21 +6546,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6570,10 +6570,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>386638</v>
+        <v>386665</v>
       </c>
       <c r="R58" t="n">
-        <v>6758463</v>
+        <v>6758445</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -6632,10 +6632,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131440209</v>
+        <v>131440212</v>
       </c>
       <c r="B59" t="n">
-        <v>79011</v>
+        <v>79254</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6643,21 +6643,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6667,10 +6667,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>386659</v>
+        <v>386638</v>
       </c>
       <c r="R59" t="n">
-        <v>6758445</v>
+        <v>6758463</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -6732,7 +6732,7 @@
         <v>131448240</v>
       </c>
       <c r="B60" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>131448198</v>
       </c>
       <c r="B61" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         <v>131448248</v>
       </c>
       <c r="B62" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 6170-2026 artfynd.xlsx
+++ b/artfynd/A 6170-2026 artfynd.xlsx
@@ -869,45 +869,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131448241</v>
+        <v>131448191</v>
       </c>
       <c r="B4" t="n">
-        <v>79254</v>
+        <v>57080</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>386485</v>
+        <v>386461</v>
       </c>
       <c r="R4" t="n">
-        <v>6758235</v>
+        <v>6758323</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -939,7 +944,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -949,7 +954,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,50 +981,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131448191</v>
+        <v>131448241</v>
       </c>
       <c r="B5" t="n">
-        <v>57080</v>
+        <v>79254</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>386461</v>
+        <v>386485</v>
       </c>
       <c r="R5" t="n">
-        <v>6758323</v>
+        <v>6758235</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131448256</v>
+        <v>131440208</v>
       </c>
       <c r="B6" t="n">
-        <v>78920</v>
+        <v>79012</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,37 +1099,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>386545</v>
+        <v>386669</v>
       </c>
       <c r="R6" t="n">
-        <v>6758481</v>
+        <v>6758449</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1156,19 +1156,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,60 +1173,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131440198</v>
+        <v>131448256</v>
       </c>
       <c r="B7" t="n">
-        <v>79278</v>
+        <v>78920</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6434</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>386498</v>
+        <v>386545</v>
       </c>
       <c r="R7" t="n">
-        <v>6758310</v>
+        <v>6758481</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1263,9 +1253,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1280,44 +1280,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131440208</v>
+        <v>131440198</v>
       </c>
       <c r="B8" t="n">
-        <v>79012</v>
+        <v>79278</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6434</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>386669</v>
+        <v>386498</v>
       </c>
       <c r="R8" t="n">
-        <v>6758449</v>
+        <v>6758310</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -2428,45 +2428,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131448243</v>
+        <v>131448252</v>
       </c>
       <c r="B19" t="n">
-        <v>79254</v>
+        <v>57080</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>386504</v>
+        <v>386539</v>
       </c>
       <c r="R19" t="n">
-        <v>6758247</v>
+        <v>6758424</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2498,7 +2503,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2508,7 +2513,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2535,7 +2540,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131448252</v>
+        <v>131448195</v>
       </c>
       <c r="B20" t="n">
         <v>57080</v>
@@ -2564,9 +2569,9 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>hona</t>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2575,10 +2580,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>386539</v>
+        <v>386371</v>
       </c>
       <c r="R20" t="n">
-        <v>6758424</v>
+        <v>6758307</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2610,7 +2615,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2620,7 +2625,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2647,50 +2652,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131448195</v>
+        <v>131448243</v>
       </c>
       <c r="B21" t="n">
-        <v>57080</v>
+        <v>79254</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>386371</v>
+        <v>386504</v>
       </c>
       <c r="R21" t="n">
-        <v>6758307</v>
+        <v>6758247</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3391,10 +3391,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131448239</v>
+        <v>131448242</v>
       </c>
       <c r="B28" t="n">
-        <v>79873</v>
+        <v>78920</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3402,21 +3402,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>386487</v>
+        <v>386479</v>
       </c>
       <c r="R28" t="n">
-        <v>6758237</v>
+        <v>6758227</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3472,6 +3472,11 @@
       <c r="AB28" t="inlineStr">
         <is>
           <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På stubbe med fem brandljud</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3498,10 +3503,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131448234</v>
+        <v>131448239</v>
       </c>
       <c r="B29" t="n">
-        <v>79254</v>
+        <v>79873</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3509,21 +3514,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3533,10 +3538,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>386438</v>
+        <v>386487</v>
       </c>
       <c r="R29" t="n">
-        <v>6758131</v>
+        <v>6758237</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3568,7 +3573,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3578,7 +3583,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3605,7 +3610,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131448194</v>
+        <v>131448234</v>
       </c>
       <c r="B30" t="n">
         <v>79254</v>
@@ -3640,10 +3645,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>386442</v>
+        <v>386438</v>
       </c>
       <c r="R30" t="n">
-        <v>6758296</v>
+        <v>6758131</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3675,7 +3680,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3685,7 +3690,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3712,7 +3717,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131448255</v>
+        <v>131448194</v>
       </c>
       <c r="B31" t="n">
         <v>79254</v>
@@ -3747,10 +3752,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>386544</v>
+        <v>386442</v>
       </c>
       <c r="R31" t="n">
-        <v>6758480</v>
+        <v>6758296</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3782,7 +3787,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3792,7 +3797,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3819,7 +3824,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131448254</v>
+        <v>131448255</v>
       </c>
       <c r="B32" t="n">
         <v>79254</v>
@@ -3854,10 +3859,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>386541</v>
+        <v>386544</v>
       </c>
       <c r="R32" t="n">
-        <v>6758426</v>
+        <v>6758480</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3889,7 +3894,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3899,7 +3904,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3926,56 +3931,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131440174</v>
+        <v>131448254</v>
       </c>
       <c r="B33" t="n">
-        <v>57080</v>
+        <v>79254</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>386653</v>
+        <v>386541</v>
       </c>
       <c r="R33" t="n">
-        <v>6758386</v>
+        <v>6758426</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4002,9 +3999,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4019,60 +4026,68 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131448242</v>
+        <v>131440174</v>
       </c>
       <c r="B34" t="n">
-        <v>78920</v>
+        <v>57080</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>386479</v>
+        <v>386653</v>
       </c>
       <c r="R34" t="n">
-        <v>6758227</v>
+        <v>6758386</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4099,24 +4114,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På stubbe med fem brandljud</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4131,12 +4131,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4770,10 +4770,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131448247</v>
+        <v>131448199</v>
       </c>
       <c r="B41" t="n">
-        <v>79254</v>
+        <v>57892</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4781,34 +4781,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>386499</v>
+        <v>386260</v>
       </c>
       <c r="R41" t="n">
-        <v>6758353</v>
+        <v>6758238</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4840,7 +4845,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4850,7 +4855,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4877,48 +4887,56 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131448236</v>
+        <v>131440177</v>
       </c>
       <c r="B42" t="n">
-        <v>79254</v>
+        <v>57080</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>386484</v>
+        <v>386568</v>
       </c>
       <c r="R42" t="n">
-        <v>6758183</v>
+        <v>6758395</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4945,19 +4963,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>14:11</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>14:11</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4972,50 +4980,50 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131448199</v>
+        <v>131448253</v>
       </c>
       <c r="B43" t="n">
-        <v>57892</v>
+        <v>57080</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5024,10 +5032,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>386260</v>
+        <v>386556</v>
       </c>
       <c r="R43" t="n">
-        <v>6758238</v>
+        <v>6758446</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5059,7 +5067,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5069,12 +5077,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5101,56 +5104,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131440177</v>
+        <v>131448247</v>
       </c>
       <c r="B44" t="n">
-        <v>57080</v>
+        <v>79254</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>386568</v>
+        <v>386499</v>
       </c>
       <c r="R44" t="n">
-        <v>6758395</v>
+        <v>6758353</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5177,9 +5172,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5194,62 +5199,57 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131448253</v>
+        <v>131448236</v>
       </c>
       <c r="B45" t="n">
-        <v>57080</v>
+        <v>79254</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>386556</v>
+        <v>386484</v>
       </c>
       <c r="R45" t="n">
-        <v>6758446</v>
+        <v>6758183</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5716,48 +5716,53 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131440159</v>
+        <v>131448235</v>
       </c>
       <c r="B50" t="n">
-        <v>79873</v>
+        <v>57080</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>386631</v>
+        <v>386484</v>
       </c>
       <c r="R50" t="n">
-        <v>6758450</v>
+        <v>6758183</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5784,9 +5789,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5801,60 +5816,68 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131448200</v>
+        <v>131440178</v>
       </c>
       <c r="B51" t="n">
-        <v>79254</v>
+        <v>57080</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>386260</v>
+        <v>386543</v>
       </c>
       <c r="R51" t="n">
-        <v>6758238</v>
+        <v>6758407</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5881,19 +5904,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>14:42</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5908,22 +5921,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131448245</v>
+        <v>131440159</v>
       </c>
       <c r="B52" t="n">
-        <v>79254</v>
+        <v>79873</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5931,37 +5944,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>386509</v>
+        <v>386631</v>
       </c>
       <c r="R52" t="n">
-        <v>6758270</v>
+        <v>6758450</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5988,19 +6001,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>14:07</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>14:07</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6015,22 +6018,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131440162</v>
+        <v>131448200</v>
       </c>
       <c r="B53" t="n">
-        <v>79873</v>
+        <v>79254</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6038,37 +6041,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>386621</v>
+        <v>386260</v>
       </c>
       <c r="R53" t="n">
-        <v>6758445</v>
+        <v>6758238</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6095,9 +6098,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6112,62 +6125,57 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131448235</v>
+        <v>131448245</v>
       </c>
       <c r="B54" t="n">
-        <v>57080</v>
+        <v>79254</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>386484</v>
+        <v>386509</v>
       </c>
       <c r="R54" t="n">
-        <v>6758183</v>
+        <v>6758270</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6199,7 +6207,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6209,7 +6217,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6236,53 +6244,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131440178</v>
+        <v>131440162</v>
       </c>
       <c r="B55" t="n">
-        <v>57080</v>
+        <v>79873</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>386543</v>
+        <v>386621</v>
       </c>
       <c r="R55" t="n">
-        <v>6758407</v>
+        <v>6758445</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>

--- a/artfynd/A 6170-2026 artfynd.xlsx
+++ b/artfynd/A 6170-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY62"/>
+  <dimension ref="A1:AY75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131440157</v>
+        <v>131448242</v>
       </c>
       <c r="B2" t="n">
-        <v>79893</v>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>386666</v>
+        <v>386479</v>
       </c>
       <c r="R2" t="n">
-        <v>6758441</v>
+        <v>6758227</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,9 +743,24 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På stubbe med fem brandljud</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,60 +775,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131440202</v>
+        <v>131448256</v>
       </c>
       <c r="B3" t="n">
-        <v>79298</v>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6434</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>386622</v>
+        <v>386545</v>
       </c>
       <c r="R3" t="n">
-        <v>6758434</v>
+        <v>6758481</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -840,9 +855,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -857,22 +882,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131448241</v>
+        <v>131448405</v>
       </c>
       <c r="B4" t="n">
-        <v>79274</v>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>386485</v>
+        <v>386711</v>
       </c>
       <c r="R4" t="n">
-        <v>6758235</v>
+        <v>6758601</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -939,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -949,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,53 +1001,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131448191</v>
+        <v>131440211</v>
       </c>
       <c r="B5" t="n">
-        <v>57100</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>386461</v>
+        <v>386633</v>
       </c>
       <c r="R5" t="n">
-        <v>6758323</v>
+        <v>6758358</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1049,19 +1069,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,60 +1086,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131448256</v>
+        <v>131440212</v>
       </c>
       <c r="B6" t="n">
-        <v>78940</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>386545</v>
+        <v>386638</v>
       </c>
       <c r="R6" t="n">
-        <v>6758481</v>
+        <v>6758463</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1156,19 +1166,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,44 +1183,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131440198</v>
+        <v>131440213</v>
       </c>
       <c r="B7" t="n">
-        <v>79298</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>386498</v>
+        <v>386650</v>
       </c>
       <c r="R7" t="n">
-        <v>6758310</v>
+        <v>6758465</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1292,32 +1292,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131440208</v>
+        <v>131440214</v>
       </c>
       <c r="B8" t="n">
-        <v>79032</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>386669</v>
+        <v>386626</v>
       </c>
       <c r="R8" t="n">
-        <v>6758449</v>
+        <v>6758448</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1389,48 +1389,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131440154</v>
+        <v>131448194</v>
       </c>
       <c r="B9" t="n">
-        <v>79893</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>386638</v>
+        <v>386442</v>
       </c>
       <c r="R9" t="n">
-        <v>6758376</v>
+        <v>6758296</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1457,9 +1457,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1474,62 +1484,57 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131448251</v>
+        <v>131448197</v>
       </c>
       <c r="B10" t="n">
-        <v>57100</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>386544</v>
+        <v>386313</v>
       </c>
       <c r="R10" t="n">
-        <v>6758394</v>
+        <v>6758273</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1561,7 +1566,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1571,7 +1576,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1598,48 +1603,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131440201</v>
+        <v>131448200</v>
       </c>
       <c r="B11" t="n">
-        <v>79298</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>386642</v>
+        <v>386260</v>
       </c>
       <c r="R11" t="n">
-        <v>6758467</v>
+        <v>6758238</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1666,9 +1671,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1683,68 +1698,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131440173</v>
+        <v>131448202</v>
       </c>
       <c r="B12" t="n">
-        <v>57100</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>386497</v>
+        <v>386233</v>
       </c>
       <c r="R12" t="n">
-        <v>6758307</v>
+        <v>6758246</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1771,9 +1778,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1788,68 +1805,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131440175</v>
+        <v>131448203</v>
       </c>
       <c r="B13" t="n">
-        <v>57100</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>386616</v>
+        <v>386191</v>
       </c>
       <c r="R13" t="n">
-        <v>6758440</v>
+        <v>6758252</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1876,9 +1885,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1893,60 +1912,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131440203</v>
+        <v>131448234</v>
       </c>
       <c r="B14" t="n">
-        <v>79298</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>386523</v>
+        <v>386438</v>
       </c>
       <c r="R14" t="n">
-        <v>6758426</v>
+        <v>6758131</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1973,9 +1992,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1990,60 +2019,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131440155</v>
+        <v>131448236</v>
       </c>
       <c r="B15" t="n">
-        <v>79893</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>386674</v>
+        <v>386484</v>
       </c>
       <c r="R15" t="n">
-        <v>6758410</v>
+        <v>6758183</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2070,9 +2099,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2087,62 +2126,57 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131448196</v>
+        <v>131448238</v>
       </c>
       <c r="B16" t="n">
-        <v>57100</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>386393</v>
+        <v>386476</v>
       </c>
       <c r="R16" t="n">
-        <v>6758306</v>
+        <v>6758198</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2174,7 +2208,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2184,7 +2218,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2211,50 +2245,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131448193</v>
+        <v>131448241</v>
       </c>
       <c r="B17" t="n">
-        <v>57100</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>386439</v>
+        <v>386485</v>
       </c>
       <c r="R17" t="n">
-        <v>6758323</v>
+        <v>6758235</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2286,7 +2315,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2296,7 +2325,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2323,56 +2352,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131440176</v>
+        <v>131448243</v>
       </c>
       <c r="B18" t="n">
-        <v>57100</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>386587</v>
+        <v>386504</v>
       </c>
       <c r="R18" t="n">
-        <v>6758386</v>
+        <v>6758247</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2399,9 +2420,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2416,62 +2447,57 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131448195</v>
+        <v>131448244</v>
       </c>
       <c r="B19" t="n">
-        <v>57100</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>386371</v>
+        <v>386492</v>
       </c>
       <c r="R19" t="n">
-        <v>6758307</v>
+        <v>6758231</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2503,7 +2529,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2513,7 +2539,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2540,50 +2566,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131448252</v>
+        <v>131448245</v>
       </c>
       <c r="B20" t="n">
-        <v>57100</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>386539</v>
+        <v>386509</v>
       </c>
       <c r="R20" t="n">
-        <v>6758424</v>
+        <v>6758270</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2615,7 +2636,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2625,7 +2646,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2652,14 +2673,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131448243</v>
+        <v>131448246</v>
       </c>
       <c r="B21" t="n">
-        <v>79274</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2687,10 +2708,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>386504</v>
+        <v>386523</v>
       </c>
       <c r="R21" t="n">
-        <v>6758247</v>
+        <v>6758350</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2722,7 +2743,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2732,7 +2753,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2759,14 +2780,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131448202</v>
+        <v>131448247</v>
       </c>
       <c r="B22" t="n">
-        <v>79274</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2794,10 +2815,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>386233</v>
+        <v>386499</v>
       </c>
       <c r="R22" t="n">
-        <v>6758246</v>
+        <v>6758353</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2829,7 +2850,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2839,7 +2860,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2866,14 +2887,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131440213</v>
+        <v>131448254</v>
       </c>
       <c r="B23" t="n">
-        <v>79274</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2897,17 +2918,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>386650</v>
+        <v>386541</v>
       </c>
       <c r="R23" t="n">
-        <v>6758465</v>
+        <v>6758426</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2934,9 +2955,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2951,26 +2982,26 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131448203</v>
+        <v>131448255</v>
       </c>
       <c r="B24" t="n">
-        <v>79274</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2998,10 +3029,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>386191</v>
+        <v>386544</v>
       </c>
       <c r="R24" t="n">
-        <v>6758252</v>
+        <v>6758480</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3033,7 +3064,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3043,7 +3074,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3070,50 +3101,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131448233</v>
+        <v>131448408</v>
       </c>
       <c r="B25" t="n">
-        <v>57100</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>386438</v>
+        <v>386711</v>
       </c>
       <c r="R25" t="n">
-        <v>6758131</v>
+        <v>6758601</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3145,7 +3171,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3155,7 +3181,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3182,50 +3208,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131448249</v>
+        <v>131448410</v>
       </c>
       <c r="B26" t="n">
-        <v>57100</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>386523</v>
+        <v>386735</v>
       </c>
       <c r="R26" t="n">
-        <v>6758378</v>
+        <v>6758583</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3257,7 +3278,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3267,7 +3288,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3294,32 +3315,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131440153</v>
+        <v>131440198</v>
       </c>
       <c r="B27" t="n">
-        <v>79893</v>
+        <v>79351</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3329,10 +3350,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>386590</v>
+        <v>386498</v>
       </c>
       <c r="R27" t="n">
-        <v>6758339</v>
+        <v>6758310</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3391,48 +3412,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131448242</v>
+        <v>131440199</v>
       </c>
       <c r="B28" t="n">
-        <v>78940</v>
+        <v>79351</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>6434</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>386479</v>
+        <v>386562</v>
       </c>
       <c r="R28" t="n">
-        <v>6758227</v>
+        <v>6758346</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3459,24 +3480,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På stubbe med fem brandljud</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3491,60 +3497,60 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131448254</v>
+        <v>131440200</v>
       </c>
       <c r="B29" t="n">
-        <v>79274</v>
+        <v>79351</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>386541</v>
+        <v>386595</v>
       </c>
       <c r="R29" t="n">
-        <v>6758426</v>
+        <v>6758342</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3571,19 +3577,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:57</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3598,60 +3594,60 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131448234</v>
+        <v>131440201</v>
       </c>
       <c r="B30" t="n">
-        <v>79274</v>
+        <v>79351</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>386438</v>
+        <v>386642</v>
       </c>
       <c r="R30" t="n">
-        <v>6758131</v>
+        <v>6758467</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3678,19 +3674,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>14:12</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>14:12</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3705,60 +3691,60 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131448239</v>
+        <v>131440202</v>
       </c>
       <c r="B31" t="n">
-        <v>79893</v>
+        <v>79351</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>386487</v>
+        <v>386622</v>
       </c>
       <c r="R31" t="n">
-        <v>6758237</v>
+        <v>6758434</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3785,19 +3771,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>14:09</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3812,60 +3788,60 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131448255</v>
+        <v>131440203</v>
       </c>
       <c r="B32" t="n">
-        <v>79274</v>
+        <v>79351</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>386544</v>
+        <v>386523</v>
       </c>
       <c r="R32" t="n">
-        <v>6758480</v>
+        <v>6758426</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3892,19 +3868,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:56</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3919,60 +3885,60 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131448194</v>
+        <v>131440207</v>
       </c>
       <c r="B33" t="n">
-        <v>79274</v>
+        <v>79351</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>386442</v>
+        <v>386494</v>
       </c>
       <c r="R33" t="n">
-        <v>6758296</v>
+        <v>6758440</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3999,49 +3965,40 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131440174</v>
+        <v>131448258</v>
       </c>
       <c r="B34" t="n">
-        <v>57100</v>
+        <v>79351</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4049,45 +4006,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>6434</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>386653</v>
+        <v>386544</v>
       </c>
       <c r="R34" t="n">
-        <v>6758386</v>
+        <v>6758480</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4114,9 +4063,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4131,22 +4090,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131448197</v>
+        <v>131440153</v>
       </c>
       <c r="B35" t="n">
-        <v>79274</v>
+        <v>79946</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4154,37 +4113,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>386313</v>
+        <v>386590</v>
       </c>
       <c r="R35" t="n">
-        <v>6758273</v>
+        <v>6758339</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4211,19 +4170,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>14:43</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4238,22 +4187,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131448192</v>
+        <v>131440154</v>
       </c>
       <c r="B36" t="n">
-        <v>79893</v>
+        <v>79946</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4281,17 +4230,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>386439</v>
+        <v>386638</v>
       </c>
       <c r="R36" t="n">
-        <v>6758323</v>
+        <v>6758376</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4318,24 +4267,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På silverlåga</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4350,22 +4284,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131440214</v>
+        <v>131440155</v>
       </c>
       <c r="B37" t="n">
-        <v>79274</v>
+        <v>79946</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4373,21 +4307,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4397,10 +4331,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>386626</v>
+        <v>386674</v>
       </c>
       <c r="R37" t="n">
-        <v>6758448</v>
+        <v>6758410</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4459,10 +4393,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131440158</v>
+        <v>131440156</v>
       </c>
       <c r="B38" t="n">
-        <v>79893</v>
+        <v>79946</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4494,10 +4428,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>386641</v>
+        <v>386665</v>
       </c>
       <c r="R38" t="n">
-        <v>6758465</v>
+        <v>6758445</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4556,48 +4490,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131448258</v>
+        <v>131440157</v>
       </c>
       <c r="B39" t="n">
-        <v>79298</v>
+        <v>79946</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>386544</v>
+        <v>386666</v>
       </c>
       <c r="R39" t="n">
-        <v>6758480</v>
+        <v>6758441</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4624,19 +4558,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:55</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4651,22 +4575,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131448250</v>
+        <v>131440158</v>
       </c>
       <c r="B40" t="n">
-        <v>79893</v>
+        <v>79946</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4694,17 +4618,17 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>386540</v>
+        <v>386641</v>
       </c>
       <c r="R40" t="n">
-        <v>6758409</v>
+        <v>6758465</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4731,19 +4655,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>13:59</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4758,22 +4672,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131448199</v>
+        <v>131440159</v>
       </c>
       <c r="B41" t="n">
-        <v>57912</v>
+        <v>79946</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4781,42 +4695,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>386260</v>
+        <v>386631</v>
       </c>
       <c r="R41" t="n">
-        <v>6758238</v>
+        <v>6758450</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4843,24 +4752,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4875,22 +4769,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131448236</v>
+        <v>131440160</v>
       </c>
       <c r="B42" t="n">
-        <v>79274</v>
+        <v>79946</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4898,37 +4792,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>386484</v>
+        <v>386635</v>
       </c>
       <c r="R42" t="n">
-        <v>6758183</v>
+        <v>6758461</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4955,19 +4849,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>14:11</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>14:11</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4982,22 +4866,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131448247</v>
+        <v>131440162</v>
       </c>
       <c r="B43" t="n">
-        <v>79274</v>
+        <v>79946</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5005,37 +4889,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>386499</v>
+        <v>386621</v>
       </c>
       <c r="R43" t="n">
-        <v>6758353</v>
+        <v>6758445</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5062,19 +4946,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>14:02</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5089,65 +4963,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131448253</v>
+        <v>131440163</v>
       </c>
       <c r="B44" t="n">
-        <v>57100</v>
+        <v>79946</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>386556</v>
+        <v>386610</v>
       </c>
       <c r="R44" t="n">
-        <v>6758446</v>
+        <v>6758401</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5174,19 +5043,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>13:57</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5201,65 +5060,57 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131440177</v>
+        <v>131440164</v>
       </c>
       <c r="B45" t="n">
-        <v>57100</v>
+        <v>79946</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>386568</v>
+        <v>386578</v>
       </c>
       <c r="R45" t="n">
-        <v>6758395</v>
+        <v>6758384</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5318,10 +5169,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131440160</v>
+        <v>131448192</v>
       </c>
       <c r="B46" t="n">
-        <v>79893</v>
+        <v>79946</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5349,17 +5200,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>386635</v>
+        <v>386439</v>
       </c>
       <c r="R46" t="n">
-        <v>6758461</v>
+        <v>6758323</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5386,9 +5237,24 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På silverlåga</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5403,22 +5269,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131448246</v>
+        <v>131448209</v>
       </c>
       <c r="B47" t="n">
-        <v>79274</v>
+        <v>79946</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5426,21 +5292,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5450,10 +5316,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>386523</v>
+        <v>386171</v>
       </c>
       <c r="R47" t="n">
-        <v>6758350</v>
+        <v>6758196</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5485,7 +5351,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5495,7 +5361,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5522,48 +5388,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131440199</v>
+        <v>131448239</v>
       </c>
       <c r="B48" t="n">
-        <v>79298</v>
+        <v>79946</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>386562</v>
+        <v>386487</v>
       </c>
       <c r="R48" t="n">
-        <v>6758346</v>
+        <v>6758237</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5590,9 +5456,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5607,22 +5483,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131440164</v>
+        <v>131448250</v>
       </c>
       <c r="B49" t="n">
-        <v>79893</v>
+        <v>79946</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5650,17 +5526,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>386578</v>
+        <v>386540</v>
       </c>
       <c r="R49" t="n">
-        <v>6758384</v>
+        <v>6758409</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5687,9 +5563,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5704,22 +5590,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131440162</v>
+        <v>131448257</v>
       </c>
       <c r="B50" t="n">
-        <v>79893</v>
+        <v>79946</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5747,17 +5633,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>386621</v>
+        <v>386534</v>
       </c>
       <c r="R50" t="n">
-        <v>6758445</v>
+        <v>6758498</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5784,9 +5670,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5801,22 +5697,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131448200</v>
+        <v>131448406</v>
       </c>
       <c r="B51" t="n">
-        <v>79274</v>
+        <v>79946</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5824,21 +5720,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5848,10 +5744,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>386260</v>
+        <v>386719</v>
       </c>
       <c r="R51" t="n">
-        <v>6758238</v>
+        <v>6758587</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5883,7 +5779,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5893,7 +5789,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5920,10 +5816,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131448245</v>
+        <v>131448199</v>
       </c>
       <c r="B52" t="n">
-        <v>79274</v>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5931,34 +5827,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>386509</v>
+        <v>386260</v>
       </c>
       <c r="R52" t="n">
-        <v>6758270</v>
+        <v>6758238</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5990,7 +5891,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6000,7 +5901,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6027,45 +5933,53 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131440159</v>
+        <v>131440173</v>
       </c>
       <c r="B53" t="n">
-        <v>79893</v>
+        <v>57141</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>386631</v>
+        <v>386497</v>
       </c>
       <c r="R53" t="n">
-        <v>6758450</v>
+        <v>6758307</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6124,10 +6038,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131448235</v>
+        <v>131440174</v>
       </c>
       <c r="B54" t="n">
-        <v>57100</v>
+        <v>57141</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6153,24 +6067,27 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>386484</v>
+        <v>386653</v>
       </c>
       <c r="R54" t="n">
-        <v>6758183</v>
+        <v>6758386</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6197,19 +6114,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>14:11</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>14:11</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6224,22 +6131,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131440178</v>
+        <v>131440175</v>
       </c>
       <c r="B55" t="n">
-        <v>57100</v>
+        <v>57141</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6279,10 +6186,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>386543</v>
+        <v>386616</v>
       </c>
       <c r="R55" t="n">
-        <v>6758407</v>
+        <v>6758440</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6341,45 +6248,53 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131440209</v>
+        <v>131440176</v>
       </c>
       <c r="B56" t="n">
-        <v>79032</v>
+        <v>57141</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>386659</v>
+        <v>386587</v>
       </c>
       <c r="R56" t="n">
-        <v>6758445</v>
+        <v>6758386</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6438,45 +6353,53 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131440163</v>
+        <v>131440177</v>
       </c>
       <c r="B57" t="n">
-        <v>79893</v>
+        <v>57141</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>386610</v>
+        <v>386568</v>
       </c>
       <c r="R57" t="n">
-        <v>6758401</v>
+        <v>6758395</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6535,45 +6458,53 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131440156</v>
+        <v>131440178</v>
       </c>
       <c r="B58" t="n">
-        <v>79893</v>
+        <v>57141</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>386665</v>
+        <v>386543</v>
       </c>
       <c r="R58" t="n">
-        <v>6758445</v>
+        <v>6758407</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -6632,48 +6563,53 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131440212</v>
+        <v>131448191</v>
       </c>
       <c r="B59" t="n">
-        <v>79274</v>
+        <v>57141</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>386638</v>
+        <v>386461</v>
       </c>
       <c r="R59" t="n">
-        <v>6758463</v>
+        <v>6758323</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6700,9 +6636,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6717,22 +6663,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131448198</v>
+        <v>131448193</v>
       </c>
       <c r="B60" t="n">
-        <v>57100</v>
+        <v>57141</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6769,10 +6715,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>386265</v>
+        <v>386439</v>
       </c>
       <c r="R60" t="n">
-        <v>6758254</v>
+        <v>6758323</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6804,7 +6750,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6814,7 +6760,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6841,10 +6787,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131448240</v>
+        <v>131448195</v>
       </c>
       <c r="B61" t="n">
-        <v>57100</v>
+        <v>57141</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6881,10 +6827,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>386487</v>
+        <v>386371</v>
       </c>
       <c r="R61" t="n">
-        <v>6758237</v>
+        <v>6758307</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6916,7 +6862,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6926,7 +6872,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6953,10 +6899,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131448248</v>
+        <v>131448196</v>
       </c>
       <c r="B62" t="n">
-        <v>57102</v>
+        <v>57141</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6993,10 +6939,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>386531</v>
+        <v>386393</v>
       </c>
       <c r="R62" t="n">
-        <v>6758378</v>
+        <v>6758306</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7028,7 +6974,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7038,7 +6984,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7062,6 +7008,1427 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>131448198</v>
+      </c>
+      <c r="B63" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Gryckheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>386265</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6758254</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>131448232</v>
+      </c>
+      <c r="B64" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Gryckheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>386417</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6758098</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>131448233</v>
+      </c>
+      <c r="B65" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Gryckheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>386438</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6758131</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>131448235</v>
+      </c>
+      <c r="B66" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Gryckheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>386484</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6758183</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>131448240</v>
+      </c>
+      <c r="B67" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Gryckheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>386487</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6758237</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>131448248</v>
+      </c>
+      <c r="B68" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Gryckheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>386531</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6758378</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>131448249</v>
+      </c>
+      <c r="B69" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Gryckheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>386523</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6758378</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>131448251</v>
+      </c>
+      <c r="B70" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Gryckheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>386544</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6758394</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>131448252</v>
+      </c>
+      <c r="B71" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Gryckheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>386539</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6758424</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>131448253</v>
+      </c>
+      <c r="B72" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Gryckheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>386556</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6758446</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>131440208</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Grycksheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>386669</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6758449</v>
+      </c>
+      <c r="S73" t="n">
+        <v>20</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>131440209</v>
+      </c>
+      <c r="B74" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Grycksheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>386659</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6758445</v>
+      </c>
+      <c r="S74" t="n">
+        <v>20</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>131448350</v>
+      </c>
+      <c r="B75" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Gryckheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>386644</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6758591</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6170-2026 artfynd.xlsx
+++ b/artfynd/A 6170-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY75"/>
+  <dimension ref="A1:AZ75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448242</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448256</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448405</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1095,6 +1115,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440211</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1192,6 +1217,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440212</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1289,6 +1319,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440213</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440214</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1493,6 +1533,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448194</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1600,6 +1645,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448197</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1707,6 +1757,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448200</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1814,6 +1869,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448202</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1921,6 +1981,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448203</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2028,6 +2093,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448234</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2135,6 +2205,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448236</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2242,6 +2317,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448238</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2349,6 +2429,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448241</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2456,6 +2541,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448243</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2563,6 +2653,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448244</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2670,6 +2765,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448245</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2777,6 +2877,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448246</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2884,6 +2989,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448247</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2991,6 +3101,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448254</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3098,6 +3213,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448255</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3205,6 +3325,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448408</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3312,6 +3437,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448410</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3409,6 +3539,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440198</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3506,6 +3641,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440199</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3603,6 +3743,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440200</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3700,6 +3845,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440201</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3797,6 +3947,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440202</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3894,6 +4049,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440203</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3992,6 +4152,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440207</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4099,6 +4264,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448258</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4196,6 +4366,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440153</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4293,6 +4468,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440154</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4390,6 +4570,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440155</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4487,6 +4672,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440156</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4584,6 +4774,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440157</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4681,6 +4876,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440158</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4778,6 +4978,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440159</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4875,6 +5080,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440160</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4972,6 +5182,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440162</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5069,6 +5284,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440163</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5166,6 +5386,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440164</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5278,6 +5503,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448192</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5385,6 +5615,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448209</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5492,6 +5727,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448239</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5599,6 +5839,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448250</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5706,6 +5951,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448257</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5813,6 +6063,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448406</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5930,6 +6185,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448199</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6035,6 +6295,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440173</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6140,6 +6405,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440174</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6245,6 +6515,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440175</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6350,6 +6625,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440176</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6455,6 +6735,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440177</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6560,6 +6845,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440178</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6672,6 +6962,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448191</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6784,6 +7079,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448193</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6896,6 +7196,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448195</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7008,6 +7313,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448196</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7120,6 +7430,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448198</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7232,6 +7547,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448232</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7344,6 +7664,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448233</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7456,6 +7781,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448235</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7568,6 +7898,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448240</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7680,6 +8015,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448248</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7792,6 +8132,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448249</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7904,6 +8249,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448251</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8016,6 +8366,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448252</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8128,6 +8483,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448253</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8225,6 +8585,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440208</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8322,6 +8687,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440209</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8429,8 +8799,89 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448350</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>